--- a/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/top-full-6.xlsx
+++ b/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/top-full-6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\przemyslaw.klys.EVOTEC\.codex\worktrees\excel-csv-quality\OfficeIMO\OfficeIMO.TestAssets\Documents\ExcelPivotCorpus\AllErrorRanking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A313570A-5BB5-4FD6-B817-79453B40FAF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE8D65D4-670F-4B7A-8DC4-239216B6B8B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{28939F35-FB4F-4A96-9EFA-DCDF0D960C6B}"/>
+    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{FEDE2983-E0E8-4ADF-B98D-EDE57C3C92E9}"/>
   </bookViews>
   <sheets>
     <sheet name="Grouped" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="167" r:id="rId3"/>
+    <pivotCache cacheId="199" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.576908449075" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{37A195EB-297A-4984-8353-B262428CF3D7}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.579479745371" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{B348DAAB-ED5E-4ADB-8B60-7663CA37B1D2}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:B8" sheet="Source"/>
   </cacheSource>
@@ -196,7 +196,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{30580A0A-C930-480D-AA26-05E480278C1C}" name="AllErrorPivot" cacheId="167" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F6D55120-38A1-4CF8-9D2E-77DE21936697}" name="AllErrorPivot" cacheId="199" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" measureFilter="1">
@@ -582,7 +582,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B7D3FE8-0425-4D69-A336-279A07BBD2BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41BF3F83-495A-4967-9F9F-542657FC8568}">
   <dimension ref="A4:B11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -660,7 +660,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58055D7C-2BF4-4440-ACE4-4EAD590B8087}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5F8EC31-4DA2-4CE1-80F3-8165F7E0CC82}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
